--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:17:08+00:00</t>
+    <t>2026-04-10T11:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-public-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-public-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
